--- a/履歴書_xx_氏名_(自己PR欄あり).xlsx
+++ b/履歴書_xx_氏名_(自己PR欄あり).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\就活\01_履歴書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\resume_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C460410-315C-429E-8516-5E7C715C9825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13672A68-0B68-44F1-A3E2-B9C41E94D1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書(左)" sheetId="1" r:id="rId1"/>
@@ -83,16 +83,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
-  <si>
-    <t xml:space="preserve">   写真を貼る位置
- 1.縦 36～40mm
-   横 24～30mm
- 2.本人 胸から上
- 3.裏面にのりづけ
- 4.裏面に氏名記入</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>履 歴 書</t>
   </si>
@@ -101,9 +115,6 @@
   </si>
   <si>
     <t>月</t>
-  </si>
-  <si>
-    <t>日現在</t>
   </si>
   <si>
     <t xml:space="preserve"> ふりがな</t>
@@ -516,62 +527,27 @@
     <phoneticPr fontId="10"/>
   </si>
   <si>
-    <t>　私が小さいころ、ゲームの中でミニゲームを作って家族や友達に遊んでもらったことがありました。その時に「面白い！」と言ってもらえてとても嬉しかったのを覚えています。高校生の時、進路に迷っている時期に参加した学校のオープンキャンパスでゲームの制作体験をしました。私は昔からゲームが大好きだったのと、小さい頃の気持ちを思い出してゲームに関わりたいと思いこの業界を目指しました。
-　専門学校では、私の制作した作品をクラスメイトや先生方から褒めていただき、自分でプログラムしたものが実際にゲームとして動き、評価してもらえることがとても面白いと思いました。なので、将来、プログラムしたものを世に出して、評価してもらいたいと思いプログラマーを目指しました。</t>
-    <rPh sb="1" eb="2">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>オモシロ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
+    <t>日現在</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>（旧校名：吉田学園情報ビジネス専門学校 2025年4月校名変更）</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　以　　上</t>
+    <rPh sb="32" eb="33">
       <t>イ</t>
     </rPh>
-    <rPh sb="67" eb="68">
-      <t>ウレ</t>
+    <rPh sb="35" eb="36">
+      <t>ウエ</t>
     </rPh>
-    <rPh sb="74" eb="75">
-      <t>オボ</t>
-    </rPh>
-    <rPh sb="81" eb="84">
-      <t>コウコウセイ</t>
-    </rPh>
-    <rPh sb="85" eb="86">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="96" eb="97">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>サンカ</t>
-    </rPh>
-    <rPh sb="129" eb="130">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="130" eb="131">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="131" eb="132">
-      <t>ムカシ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>ダイス</t>
-    </rPh>
-    <rPh sb="149" eb="150">
-      <t>コロ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>ダイス</t>
-    </rPh>
-    <rPh sb="266" eb="267">
-      <t>オモ</t>
-    </rPh>
-    <rPh sb="295" eb="297">
-      <t>ヒョウカ</t>
-    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>　私が小さいころ、ゲームの中でミニゲームを作って家族や友達に遊んでもらったことがありました。その時に「面白い！」と言ってもらえてとても嬉しかったのを覚えています。高校生の時、進路に迷っている時期に参加した学校のオープンキャンパスでゲームの制作体験をしました。私は昔からゲームが大好きだったのと、小さい頃の気持ちを思い出してゲームに関わりたいと思いこの業界を目指しました。
+　専門学校では、先輩方や先生方に質問し、添削をしてもらいながら制作することを心がけました。その結果、多くの人から高評価をいただき、自分でプログラムしたものが実際にゲームとして動き、評価してもらえることがとても面白いと思いました。なので、将来、プログラムしたものを世に出して、評価してもらいたいと思いプログラマーを目指しました。
+　</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1322,7 +1298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1416,75 +1392,62 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1502,43 +1465,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1560,9 +1545,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1638,6 +1620,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1904,8 +1950,8 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="75" t="s">
-        <v>0</v>
+      <c r="Q2" s="70" t="e" vm="1">
+        <v>#VALUE!</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -1920,10 +1966,10 @@
     </row>
     <row r="3" spans="1:27" ht="16.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="53" t="s">
-        <v>1</v>
+      <c r="B3" s="75" t="s">
+        <v>0</v>
       </c>
-      <c r="C3" s="54"/>
+      <c r="C3" s="39"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1936,7 +1982,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="54"/>
+      <c r="Q3" s="39"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -1950,34 +1996,34 @@
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" thickBot="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
       <c r="D4" s="25"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="33"/>
-      <c r="I4" s="62">
+      <c r="I4" s="81">
         <v>2025</v>
       </c>
-      <c r="J4" s="63"/>
+      <c r="J4" s="82"/>
       <c r="K4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="19">
+        <v>12</v>
+      </c>
+      <c r="M4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="19">
-        <v>7</v>
-      </c>
-      <c r="M4" s="34" t="s">
+      <c r="N4" s="19">
         <v>3</v>
       </c>
-      <c r="N4" s="19">
-        <v>7</v>
-      </c>
       <c r="O4" s="2" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="P4" s="1"/>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="39"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1992,25 +2038,25 @@
     <row r="5" spans="1:27" ht="16.5" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
-      <c r="C5" s="56" t="s">
-        <v>33</v>
+      <c r="C5" s="76" t="s">
+        <v>31</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="58"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="78"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="54"/>
+      <c r="Q5" s="39"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -2025,25 +2071,25 @@
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
-      <c r="C6" s="59" t="s">
-        <v>32</v>
+      <c r="C6" s="79" t="s">
+        <v>30</v>
       </c>
-      <c r="D6" s="59"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="61"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="80"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="54"/>
+      <c r="Q6" s="39"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -2058,21 +2104,21 @@
     <row r="7" spans="1:27" ht="23" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="63"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="54"/>
+      <c r="Q7" s="39"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -2087,39 +2133,39 @@
     <row r="8" spans="1:27" ht="10.25" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="64">
+      <c r="C8" s="83">
         <v>2006</v>
       </c>
-      <c r="D8" s="64"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="65"/>
-      <c r="F8" s="70" t="s">
-        <v>2</v>
+      <c r="F8" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="G8" s="65">
         <v>1</v>
       </c>
-      <c r="H8" s="70" t="s">
-        <v>3</v>
+      <c r="H8" s="64" t="s">
+        <v>2</v>
       </c>
       <c r="I8" s="65">
         <v>23</v>
       </c>
-      <c r="J8" s="70" t="s">
+      <c r="J8" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="69">
+        <v>19</v>
+      </c>
+      <c r="N8" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="74">
-        <v>19</v>
-      </c>
-      <c r="N8" s="70" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="31" t="s">
-        <v>9</v>
-      </c>
       <c r="P8" s="1"/>
-      <c r="Q8" s="54"/>
+      <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -2134,20 +2180,20 @@
     <row r="9" spans="1:27" ht="20" customHeight="1" thickBot="1">
       <c r="A9" s="1"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
       <c r="O9" s="32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -2165,28 +2211,28 @@
     <row r="10" spans="1:27" ht="16.5" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
-      <c r="C10" s="76" t="s">
-        <v>37</v>
+      <c r="C10" s="71" t="s">
+        <v>35</v>
       </c>
-      <c r="D10" s="76"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="67" t="s">
-        <v>10</v>
+      <c r="D10" s="71"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="85" t="s">
+        <v>8</v>
       </c>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="58"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="78"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -2200,28 +2246,28 @@
     <row r="11" spans="1:27" ht="16.5" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="72" t="s">
-        <v>35</v>
+      <c r="E11" s="67" t="s">
+        <v>33</v>
       </c>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="79"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="50"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -2234,27 +2280,27 @@
     </row>
     <row r="12" spans="1:27" ht="16.5" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="47" t="s">
-        <v>36</v>
+      <c r="B12" s="72" t="s">
+        <v>34</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="50" t="s">
-        <v>13</v>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="40" t="s">
+        <v>11</v>
       </c>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="52"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -2268,28 +2314,28 @@
     <row r="13" spans="1:27" ht="16.5" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
-      <c r="C13" s="90" t="s">
-        <v>38</v>
+      <c r="C13" s="35" t="s">
+        <v>36</v>
       </c>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="92"/>
-      <c r="P13" s="77" t="s">
-        <v>34</v>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="48" t="s">
+        <v>32</v>
       </c>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="79"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="50"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -2303,26 +2349,26 @@
     <row r="14" spans="1:27" ht="16.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="50" t="s">
-        <v>15</v>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="40" t="s">
+        <v>13</v>
       </c>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="52"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="42"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -2336,28 +2382,28 @@
     <row r="15" spans="1:27" ht="16.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="94" t="s">
-        <v>16</v>
+      <c r="E15" s="67"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="43" t="s">
+        <v>14</v>
       </c>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="95"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="82"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="47"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -2370,23 +2416,23 @@
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="82"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="47"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -2399,23 +2445,23 @@
     </row>
     <row r="17" spans="1:27" ht="16.5" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="86"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="57"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -2458,28 +2504,28 @@
     <row r="19" spans="1:27" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>3</v>
+      <c r="D19" s="26"/>
+      <c r="E19" s="58" t="s">
+        <v>15</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="89"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="59"/>
+      <c r="R19" s="60"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -2494,25 +2540,25 @@
       <c r="A20" s="1"/>
       <c r="B20" s="12"/>
       <c r="C20" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D20" s="27"/>
-      <c r="E20" s="38" t="s">
-        <v>31</v>
+      <c r="E20" s="61" t="s">
+        <v>29</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="40"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="63"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -2532,22 +2578,22 @@
         <v>3</v>
       </c>
       <c r="D21" s="27"/>
-      <c r="E21" s="38" t="s">
-        <v>39</v>
+      <c r="E21" s="61" t="s">
+        <v>37</v>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="40"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="63"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -2567,22 +2613,22 @@
         <v>4</v>
       </c>
       <c r="D22" s="27"/>
-      <c r="E22" s="38" t="s">
-        <v>40</v>
+      <c r="E22" s="61" t="s">
+        <v>38</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="40"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="63"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -2602,22 +2648,22 @@
         <v>3</v>
       </c>
       <c r="D23" s="27"/>
-      <c r="E23" s="38" t="s">
-        <v>41</v>
+      <c r="E23" s="61" t="s">
+        <v>39</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="40"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="63"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -2637,22 +2683,22 @@
         <v>4</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="38" t="s">
-        <v>42</v>
+      <c r="E24" s="61" t="s">
+        <v>40</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="40"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="63"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -2672,22 +2718,22 @@
         <v>3</v>
       </c>
       <c r="D25" s="27"/>
-      <c r="E25" s="38" t="s">
-        <v>43</v>
+      <c r="E25" s="61" t="s">
+        <v>41</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="40"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="62"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="63"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -2703,22 +2749,22 @@
       <c r="B26" s="12"/>
       <c r="C26" s="13"/>
       <c r="D26" s="27"/>
-      <c r="E26" s="41" t="s">
-        <v>44</v>
+      <c r="E26" s="90" t="s">
+        <v>50</v>
       </c>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="43"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="92"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
@@ -2731,29 +2777,25 @@
     </row>
     <row r="27" spans="1:27" ht="25.5" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="12">
-        <v>2024</v>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="93" t="s">
+        <v>42</v>
       </c>
-      <c r="C27" s="13">
-        <v>4</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="40"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="95"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -2766,23 +2808,27 @@
     </row>
     <row r="28" spans="1:27" ht="25.5" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="12"/>
+      <c r="B28" s="12">
+        <v>2024</v>
+      </c>
       <c r="C28" s="13"/>
       <c r="D28" s="27"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="40"/>
+      <c r="E28" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="62"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="62"/>
+      <c r="R28" s="63"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
@@ -2798,20 +2844,22 @@
       <c r="B29" s="12"/>
       <c r="C29" s="13"/>
       <c r="D29" s="27"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="40"/>
+      <c r="E29" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="63"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
@@ -2827,20 +2875,20 @@
       <c r="B30" s="14"/>
       <c r="C30" s="13"/>
       <c r="D30" s="27"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="40"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="63"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
@@ -2856,20 +2904,20 @@
       <c r="B31" s="15"/>
       <c r="C31" s="29"/>
       <c r="D31" s="30"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="40"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="63"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
@@ -2883,26 +2931,26 @@
     <row r="32" spans="1:27" ht="25.5" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" s="27"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="46"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="98"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
@@ -2918,22 +2966,22 @@
       <c r="B33" s="12"/>
       <c r="C33" s="13"/>
       <c r="D33" s="27"/>
-      <c r="E33" s="38" t="s">
-        <v>18</v>
+      <c r="E33" s="61" t="s">
+        <v>16</v>
       </c>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
-      <c r="Q33" s="39"/>
-      <c r="R33" s="40"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
+      <c r="R33" s="63"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
@@ -2947,28 +2995,28 @@
     <row r="34" spans="1:27" ht="25.5" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D34" s="27"/>
-      <c r="E34" s="38" t="s">
-        <v>19</v>
+      <c r="E34" s="61" t="s">
+        <v>17</v>
       </c>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="40"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
+      <c r="M34" s="62"/>
+      <c r="N34" s="62"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="62"/>
+      <c r="Q34" s="62"/>
+      <c r="R34" s="63"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
@@ -2982,28 +3030,28 @@
     <row r="35" spans="1:27" ht="25.5" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" s="27"/>
-      <c r="E35" s="38" t="s">
-        <v>19</v>
+      <c r="E35" s="61" t="s">
+        <v>17</v>
       </c>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
-      <c r="Q35" s="39"/>
-      <c r="R35" s="40"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="63"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
@@ -3017,28 +3065,28 @@
     <row r="36" spans="1:27" ht="25.5" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D36" s="28"/>
-      <c r="E36" s="35" t="s">
-        <v>19</v>
+      <c r="E36" s="87" t="s">
+        <v>17</v>
       </c>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="36"/>
-      <c r="P36" s="36"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="37"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+      <c r="K36" s="88"/>
+      <c r="L36" s="88"/>
+      <c r="M36" s="88"/>
+      <c r="N36" s="88"/>
+      <c r="O36" s="88"/>
+      <c r="P36" s="88"/>
+      <c r="Q36" s="88"/>
+      <c r="R36" s="89"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
@@ -3052,7 +3100,7 @@
     <row r="37" spans="1:27" ht="28.25" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -31009,17 +31057,28 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C13:O13"/>
-    <mergeCell ref="C14:O14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="H15:O15"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="B16:O16"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="B17:O17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="E19:R19"/>
+    <mergeCell ref="E36:R36"/>
+    <mergeCell ref="E24:R24"/>
+    <mergeCell ref="E25:R25"/>
+    <mergeCell ref="E26:R26"/>
+    <mergeCell ref="E27:R27"/>
+    <mergeCell ref="E28:R28"/>
+    <mergeCell ref="E29:R29"/>
+    <mergeCell ref="E30:R30"/>
+    <mergeCell ref="E31:R31"/>
+    <mergeCell ref="E32:R32"/>
+    <mergeCell ref="E33:R33"/>
+    <mergeCell ref="E34:R34"/>
+    <mergeCell ref="E35:R35"/>
+    <mergeCell ref="B12:O12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="C5:O5"/>
+    <mergeCell ref="C6:O7"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C8:E9"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="H11:O11"/>
     <mergeCell ref="E20:R20"/>
     <mergeCell ref="E21:R21"/>
     <mergeCell ref="E22:R22"/>
@@ -31036,28 +31095,17 @@
     <mergeCell ref="Q2:Q8"/>
     <mergeCell ref="C10:O10"/>
     <mergeCell ref="P11:R11"/>
-    <mergeCell ref="B12:O12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="C5:O5"/>
-    <mergeCell ref="C6:O7"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C8:E9"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="H11:O11"/>
-    <mergeCell ref="E36:R36"/>
-    <mergeCell ref="E24:R24"/>
-    <mergeCell ref="E25:R25"/>
-    <mergeCell ref="E26:R26"/>
-    <mergeCell ref="E27:R27"/>
-    <mergeCell ref="E28:R28"/>
-    <mergeCell ref="E29:R29"/>
-    <mergeCell ref="E30:R30"/>
-    <mergeCell ref="E31:R31"/>
-    <mergeCell ref="E32:R32"/>
-    <mergeCell ref="E33:R33"/>
-    <mergeCell ref="E34:R34"/>
-    <mergeCell ref="E35:R35"/>
+    <mergeCell ref="B16:O16"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="E19:R19"/>
+    <mergeCell ref="C13:O13"/>
+    <mergeCell ref="C14:O14"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="H15:O15"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="P13:R13"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <hyperlinks>
@@ -31123,21 +31171,21 @@
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="96" t="s">
-        <v>22</v>
+      <c r="B2" s="99" t="s">
+        <v>20</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="60"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -31155,21 +31203,21 @@
     </row>
     <row r="3" spans="1:28" ht="16.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="97" t="s">
-        <v>23</v>
+      <c r="B3" s="100" t="s">
+        <v>21</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="99"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="102"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
@@ -31188,20 +31236,20 @@
     <row r="4" spans="1:28" ht="30" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
-      <c r="C4" s="107" t="s">
-        <v>49</v>
+      <c r="C4" s="90" t="s">
+        <v>47</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="111"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -31219,21 +31267,21 @@
     </row>
     <row r="5" spans="1:28" ht="16.5" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="97" t="s">
-        <v>24</v>
+      <c r="B5" s="100" t="s">
+        <v>22</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="99"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="102"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -31252,20 +31300,20 @@
     <row r="6" spans="1:28" ht="30" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="107" t="s">
-        <v>47</v>
+      <c r="C6" s="90" t="s">
+        <v>45</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="111"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -31283,21 +31331,21 @@
     </row>
     <row r="7" spans="1:28" ht="16.5" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="97" t="s">
-        <v>25</v>
+      <c r="B7" s="100" t="s">
+        <v>23</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="99"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="102"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -31316,20 +31364,20 @@
     <row r="8" spans="1:28" ht="30" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="107" t="s">
-        <v>46</v>
+      <c r="C8" s="90" t="s">
+        <v>44</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="108"/>
-      <c r="N8" s="109"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="111"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -31347,21 +31395,21 @@
     </row>
     <row r="9" spans="1:28" ht="16.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="97" t="s">
-        <v>26</v>
+      <c r="B9" s="100" t="s">
+        <v>24</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="99"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="102"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -31380,20 +31428,20 @@
     <row r="10" spans="1:28" ht="30" customHeight="1" thickBot="1">
       <c r="A10" s="1"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="117" t="s">
-        <v>48</v>
+      <c r="C10" s="119" t="s">
+        <v>46</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="121"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -31441,21 +31489,21 @@
     </row>
     <row r="12" spans="1:28" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="120" t="s">
-        <v>29</v>
+      <c r="B12" s="122" t="s">
+        <v>27</v>
       </c>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="124"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -31473,21 +31521,21 @@
     </row>
     <row r="13" spans="1:28" ht="25.5" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="123" t="s">
-        <v>50</v>
+      <c r="B13" s="125" t="s">
+        <v>48</v>
       </c>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="125"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="127"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -31505,19 +31553,19 @@
     </row>
     <row r="14" spans="1:28" ht="25.5" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="123"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="125"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="126"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="127"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -31535,19 +31583,19 @@
     </row>
     <row r="15" spans="1:28" ht="25.5" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="125"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+      <c r="M15" s="126"/>
+      <c r="N15" s="127"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -31565,19 +31613,19 @@
     </row>
     <row r="16" spans="1:28" ht="25.5" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="124"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="125"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="127"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -31595,19 +31643,19 @@
     </row>
     <row r="17" spans="1:28" ht="25.5" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="123"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="125"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="127"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -31625,19 +31673,19 @@
     </row>
     <row r="18" spans="1:28" ht="25.5" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="123"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="125"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="126"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="126"/>
+      <c r="N18" s="127"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -31655,19 +31703,19 @@
     </row>
     <row r="19" spans="1:28" ht="32" customHeight="1" thickBot="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="128"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="129"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="129"/>
+      <c r="K19" s="129"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="129"/>
+      <c r="N19" s="130"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -31713,21 +31761,21 @@
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="120" t="s">
-        <v>27</v>
+      <c r="B21" s="122" t="s">
+        <v>25</v>
       </c>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="121"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="124"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -31745,21 +31793,21 @@
     </row>
     <row r="22" spans="1:28" ht="22.25" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="104" t="s">
-        <v>51</v>
+      <c r="B22" s="107" t="s">
+        <v>52</v>
       </c>
-      <c r="C22" s="100"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="110"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="111"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="113"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -31777,19 +31825,19 @@
     </row>
     <row r="23" spans="1:28" ht="22.25" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="111"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="113"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -31807,19 +31855,19 @@
     </row>
     <row r="24" spans="1:28" ht="22.25" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="113"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="111"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="113"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -31837,19 +31885,19 @@
     </row>
     <row r="25" spans="1:28" ht="22.25" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="112"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="113"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -31867,19 +31915,19 @@
     </row>
     <row r="26" spans="1:28" ht="22.25" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="112"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="110"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="111"/>
+      <c r="B26" s="114"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="113"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -31897,19 +31945,19 @@
     </row>
     <row r="27" spans="1:28" ht="22.25" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="112"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="111"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="113"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -31925,21 +31973,21 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="22.25" customHeight="1" thickBot="1">
+    <row r="28" spans="1:28" ht="12.5" customHeight="1" thickBot="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="114"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="116"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="118"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -31987,21 +32035,21 @@
     </row>
     <row r="30" spans="1:28" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="120" t="s">
-        <v>28</v>
+      <c r="B30" s="122" t="s">
+        <v>26</v>
       </c>
-      <c r="C30" s="121"/>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
-      <c r="I30" s="121"/>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="122"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="123"/>
+      <c r="J30" s="123"/>
+      <c r="K30" s="123"/>
+      <c r="L30" s="123"/>
+      <c r="M30" s="123"/>
+      <c r="N30" s="124"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -32019,19 +32067,19 @@
     </row>
     <row r="31" spans="1:28" ht="19.5" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="104"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="101"/>
+      <c r="B31" s="107"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="104"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -32049,19 +32097,19 @@
     </row>
     <row r="32" spans="1:28" ht="19.5" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="54"/>
-      <c r="N32" s="101"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="104"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -32079,19 +32127,19 @@
     </row>
     <row r="33" spans="1:28" ht="19.5" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="101"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="104"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -32109,19 +32157,19 @@
     </row>
     <row r="34" spans="1:28" ht="19.5" customHeight="1" thickBot="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
-      <c r="N34" s="103"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="106"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -61055,6 +61103,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="00d5623e-072c-4ad5-912d-26bd97b5db83" xsi:nil="true"/>
@@ -61063,15 +61120,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61304,20 +61352,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E86C847F-B98E-4A05-9B1A-14EABAE03229}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E146B384-79D2-459D-9078-8DC184935C68}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="00d5623e-072c-4ad5-912d-26bd97b5db83"/>
     <ds:schemaRef ds:uri="83781a9d-2ef9-4448-9205-848dfcc1757c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E86C847F-B98E-4A05-9B1A-14EABAE03229}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
